--- a/data/reference/inventory/gsa-001/2026-08-02/ARPI_Granite_Chevrolet_Inventory_Sanitized_2026-08-02.xlsx
+++ b/data/reference/inventory/gsa-001/2026-08-02/ARPI_Granite_Chevrolet_Inventory_Sanitized_2026-08-02.xlsx
@@ -1614,7 +1614,7 @@
         <x:v>Dealer group</x:v>
       </x:c>
       <x:c r="B5" s="19" t="str">
-        <x:v>Granite State Auto Group</x:v>
+        <x:v>Granite Auto Group</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
@@ -1850,7 +1850,7 @@
         <x:v>Recommended repository path</x:v>
       </x:c>
       <x:c r="B30" s="58" t="str">
-        <x:v>data/reference/inventory/gsa-001/2026-08-02/granite-chevrolet-inventory-sanitized.xlsx</x:v>
+        <x:v>data/reference/inventory/gsa-001/2026-08-02/ARPI_Granite_Chevrolet_Inventory_Sanitized_2026-08-02.xlsx</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="34" customHeight="1">
@@ -1866,7 +1866,7 @@
         <x:v>Intended adapter</x:v>
       </x:c>
       <x:c r="B32" s="60" t="str">
-        <x:v>scripts/import_inventory_snapshot.py</x:v>
+        <x:v>portfolio/scripts/generate-inventory-data.ts</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="34" customHeight="1">
@@ -1917,7 +1917,7 @@
     </x:row>
     <x:row r="38" ht="28" customHeight="1">
       <x:c r="A38" s="355" t="str">
-        <x:v>Granite State Auto Group and Granite Chevrolet of Nashua are fictional. Original VINs, source URLs, street address, and real dealership identity have been removed. This workbook is not fully synthetic: model, trim, mileage, condition, advertised-price, and inventory-mix attributes are retained from a de-identified public reference snapshot. Do not present these rows as current dealership performance, confidential operational data, completed sales, or transaction results.</x:v>
+        <x:v>Granite Auto Group and Granite Chevrolet of Nashua are fictional. Original VINs, source URLs, street address, and real dealership identity have been removed. This workbook is not fully synthetic: model, trim, mileage, condition, advertised-price, and inventory-mix attributes are retained from a de-identified public reference snapshot. Do not present these rows as current dealership performance, confidential operational data, completed sales, or transaction results.</x:v>
       </x:c>
       <x:c r="B38" s="356"/>
       <x:c r="C38" s="356"/>
@@ -2016,7 +2016,7 @@
         <x:v>Dealer group</x:v>
       </x:c>
       <x:c r="B4" s="17" t="str">
-        <x:v>Granite State Auto Group</x:v>
+        <x:v>Granite Auto Group</x:v>
       </x:c>
       <x:c r="D4" s="165" t="str">
         <x:v>Condition</x:v>
@@ -2400,7 +2400,7 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="256" t="str">
-        <x:v>Granite State Auto Group and its stores are fictional. Original VINs and source URLs are removed, but listing attributes remain a de-identified public reference snapshot. Use the README sheet for the governance requirement, repository path, and ingestion contract.</x:v>
+        <x:v>Granite Auto Group and its stores are fictional. Original VINs and source URLs are removed, but listing attributes remain a de-identified public reference snapshot. Use the README sheet for the governance requirement, repository path, and ingestion contract.</x:v>
       </x:c>
       <x:c r="B39" s="257"/>
       <x:c r="C39" s="257"/>
